--- a/artfynd/A 59732-2021 artfynd.xlsx
+++ b/artfynd/A 59732-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121454625</v>
       </c>
       <c r="B2" t="n">
-        <v>109005</v>
+        <v>109018</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>121454724</v>
       </c>
       <c r="B3" t="n">
-        <v>105099</v>
+        <v>105112</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 59732-2021 artfynd.xlsx
+++ b/artfynd/A 59732-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121454625</v>
+        <v>121454724</v>
       </c>
       <c r="B2" t="n">
-        <v>109018</v>
+        <v>105113</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220320</v>
+        <v>221141</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ängsskära</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Serratula tinctoria</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121454724</v>
+        <v>121454625</v>
       </c>
       <c r="B3" t="n">
-        <v>105112</v>
+        <v>109019</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,20 +794,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221141</v>
+        <v>220320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Ängsskära</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Serratula tinctoria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">

--- a/artfynd/A 59732-2021 artfynd.xlsx
+++ b/artfynd/A 59732-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121454724</v>
       </c>
       <c r="B2" t="n">
-        <v>105113</v>
+        <v>105116</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>121454625</v>
       </c>
       <c r="B3" t="n">
-        <v>109019</v>
+        <v>109022</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 59732-2021 artfynd.xlsx
+++ b/artfynd/A 59732-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121454724</v>
+        <v>121454625</v>
       </c>
       <c r="B2" t="n">
-        <v>105116</v>
+        <v>109028</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221141</v>
+        <v>220320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Ängsskära</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Serratula tinctoria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121454625</v>
+        <v>121454724</v>
       </c>
       <c r="B3" t="n">
-        <v>109022</v>
+        <v>105122</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,20 +794,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220320</v>
+        <v>221141</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ängsskära</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Serratula tinctoria</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">

--- a/artfynd/A 59732-2021 artfynd.xlsx
+++ b/artfynd/A 59732-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121454625</v>
       </c>
       <c r="B2" t="n">
-        <v>109028</v>
+        <v>109029</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>121454724</v>
       </c>
       <c r="B3" t="n">
-        <v>105122</v>
+        <v>105123</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 59732-2021 artfynd.xlsx
+++ b/artfynd/A 59732-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121454625</v>
+        <v>121454724</v>
       </c>
       <c r="B2" t="n">
-        <v>109029</v>
+        <v>105123</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220320</v>
+        <v>221141</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ängsskära</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Serratula tinctoria</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121454724</v>
+        <v>121454625</v>
       </c>
       <c r="B3" t="n">
-        <v>105123</v>
+        <v>109029</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,20 +794,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221141</v>
+        <v>220320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Ängsskära</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Serratula tinctoria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">

--- a/artfynd/A 59732-2021 artfynd.xlsx
+++ b/artfynd/A 59732-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121454724</v>
+        <v>121454625</v>
       </c>
       <c r="B2" t="n">
-        <v>105123</v>
+        <v>109029</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221141</v>
+        <v>220320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Ängsskära</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Serratula tinctoria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121454625</v>
+        <v>121454724</v>
       </c>
       <c r="B3" t="n">
-        <v>109029</v>
+        <v>105123</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,20 +794,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220320</v>
+        <v>221141</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ängsskära</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Serratula tinctoria</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">

--- a/artfynd/A 59732-2021 artfynd.xlsx
+++ b/artfynd/A 59732-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121454625</v>
+        <v>121454724</v>
       </c>
       <c r="B2" t="n">
-        <v>109037</v>
+        <v>105131</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220320</v>
+        <v>221141</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ängsskära</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Serratula tinctoria</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121454724</v>
+        <v>121454625</v>
       </c>
       <c r="B3" t="n">
-        <v>105131</v>
+        <v>109037</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,20 +794,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221141</v>
+        <v>220320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Ängsskära</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Serratula tinctoria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
